--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.77086355281492</v>
+        <v>11.82526532733242</v>
       </c>
       <c r="D2" t="n">
-        <v>50.71426543376354</v>
+        <v>8.241068132986577</v>
       </c>
       <c r="E2" t="n">
-        <v>15.05286918667441</v>
+        <v>2.446091242834592</v>
       </c>
       <c r="F2" t="n">
-        <v>19.01558839473703</v>
+        <v>3.090033114144768</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.68649673837093</v>
+        <v>5.636555719985277</v>
       </c>
       <c r="D3" t="n">
-        <v>34.54562667035069</v>
+        <v>5.613664333931988</v>
       </c>
       <c r="E3" t="n">
-        <v>15.05286918667441</v>
+        <v>2.446091242834592</v>
       </c>
       <c r="F3" t="n">
-        <v>19.01558839473703</v>
+        <v>3.090033114144768</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.9394776645957</v>
+        <v>10.0651651204968</v>
       </c>
       <c r="D4" t="n">
-        <v>5.876787417266305</v>
+        <v>0.9549779553057747</v>
       </c>
       <c r="E4" t="n">
-        <v>15.05286918667441</v>
+        <v>2.446091242834592</v>
       </c>
       <c r="F4" t="n">
-        <v>19.01558839473703</v>
+        <v>3.090033114144768</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>69.94157584127989</v>
+        <v>11.36550607420798</v>
       </c>
       <c r="D5" t="n">
-        <v>6.852222110075313</v>
+        <v>1.113486092887238</v>
       </c>
       <c r="E5" t="n">
-        <v>15.05286918667441</v>
+        <v>2.446091242834592</v>
       </c>
       <c r="F5" t="n">
-        <v>19.01558839473703</v>
+        <v>3.090033114144768</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
